--- a/tests/fixtures/comb_z1_2026-04-10.xlsx
+++ b/tests/fixtures/comb_z1_2026-04-10.xlsx
@@ -1885,7 +1885,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1901,17 +1901,27 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>pertype</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>period</t>
-        </is>
-      </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>rolly_amt</t>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>qrtr_target</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>rolly_target</t>
         </is>
       </c>
     </row>
@@ -1923,21 +1933,27 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2019-4</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>q2019-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>120</v>
+        <v>160</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="3">
@@ -1948,21 +1964,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>q2020-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>160</v>
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="4">
@@ -1973,21 +1995,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>148</v>
+        <v>125</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>205</v>
       </c>
     </row>
     <row r="5">
@@ -1998,21 +2026,27 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>q2020-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>140</v>
+        <v>156</v>
+      </c>
+      <c r="F5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G5" t="n">
+        <v>196</v>
       </c>
     </row>
     <row r="6">
@@ -2023,21 +2057,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-4</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>q2020-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>138</v>
+        <v>195</v>
+      </c>
+      <c r="F6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G6" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="7">
@@ -2048,21 +2088,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-1</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>q2021-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>168</v>
+        <v>125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>125</v>
+      </c>
+      <c r="G7" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="8">
@@ -2073,21 +2119,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>q2021-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>175</v>
+        <v>156</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="9">
@@ -2098,21 +2150,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>q2021-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>184</v>
+        <v>195</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39</v>
+      </c>
+      <c r="G9" t="n">
+        <v>234</v>
       </c>
     </row>
     <row r="10">
@@ -2123,21 +2181,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-4</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>q2021-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>195</v>
+        <v>244</v>
+      </c>
+      <c r="F10" t="n">
+        <v>49</v>
+      </c>
+      <c r="G10" t="n">
+        <v>244</v>
       </c>
     </row>
     <row r="11">
@@ -2148,21 +2212,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>costs</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2022-1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>q2022-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220</v>
+        <v>150</v>
+      </c>
+      <c r="F11" t="n">
+        <v>150</v>
+      </c>
+      <c r="G11" t="n">
+        <v>269</v>
       </c>
     </row>
     <row r="12">
@@ -2173,21 +2243,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2019-4</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>q2019-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>160</v>
+        <v>120</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="13">
@@ -2198,21 +2274,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-1</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>q2020-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220</v>
+        <v>70</v>
+      </c>
+      <c r="F13" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" t="n">
+        <v>160</v>
       </c>
     </row>
     <row r="14">
@@ -2223,21 +2305,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>205</v>
+        <v>88</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>148</v>
       </c>
     </row>
     <row r="15">
@@ -2248,21 +2336,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-3</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>q2020-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>196</v>
+        <v>110</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22</v>
+      </c>
+      <c r="G15" t="n">
+        <v>140</v>
       </c>
     </row>
     <row r="16">
@@ -2273,21 +2367,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>q2020-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>195</v>
+        <v>138</v>
+      </c>
+      <c r="F16" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" t="n">
+        <v>138</v>
       </c>
     </row>
     <row r="17">
@@ -2298,21 +2398,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-1</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>q2021-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220</v>
+        <v>100</v>
+      </c>
+      <c r="F17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" t="n">
+        <v>168</v>
       </c>
     </row>
     <row r="18">
@@ -2323,21 +2429,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>q2021-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>226</v>
+        <v>125</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" t="n">
+        <v>175</v>
       </c>
     </row>
     <row r="19">
@@ -2348,21 +2460,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-3</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>q2021-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>234</v>
+        <v>156</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>184</v>
       </c>
     </row>
     <row r="20">
@@ -2373,21 +2491,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>q2021-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>244</v>
+        <v>195</v>
+      </c>
+      <c r="F20" t="n">
+        <v>39</v>
+      </c>
+      <c r="G20" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="21">
@@ -2398,47 +2522,55 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2022-1</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>q2022-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>269</v>
+        <v>125</v>
+      </c>
+      <c r="F21" t="n">
+        <v>125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>cieB</t>
+          <t>cieA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sales</t>
+          <t>costs</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2022-2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>q2020-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>125</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2453,16 +2585,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2020-4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>q2020-3</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>156</v>
+        <v>195</v>
+      </c>
+      <c r="F23" t="n">
+        <v>39</v>
+      </c>
+      <c r="G23" t="n">
+        <v>195</v>
       </c>
     </row>
     <row r="24">
@@ -2478,16 +2616,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>q2020-4</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>195</v>
+        <v>156</v>
+      </c>
+      <c r="F24" t="n">
+        <v>31</v>
+      </c>
+      <c r="G24" t="n">
+        <v>226</v>
       </c>
     </row>
     <row r="25">
@@ -2503,22 +2647,26 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-4</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>q2021-1</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>320</v>
+        <v>244</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>244</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>cieB</t>
+          <t>cieC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2528,266 +2676,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cum</t>
+          <t>q2021-4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>q2021-2</t>
+          <t>cum</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>cieB</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>q2021-3</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>cieB</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>q2021-4</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
         <v>244</v>
       </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>cieB</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>q2022-1</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>q2020-2</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>q2020-3</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>q2021-1</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>q2021-2</t>
-        </is>
-      </c>
-      <c r="E33" t="n">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>q2021-3</t>
-        </is>
-      </c>
-      <c r="E34" t="n">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>q2021-4</t>
-        </is>
-      </c>
-      <c r="E35" t="n">
+      <c r="F26" t="n">
+        <v>49</v>
+      </c>
+      <c r="G26" t="n">
         <v>244</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>cieC</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>sales</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>cum</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>q2022-1</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/tests/fixtures/comb_z1_2026-04-10.xlsx
+++ b/tests/fixtures/comb_z1_2026-04-10.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="invalid_data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="valid_data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="output" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/tests/fixtures/comb_z1_2026-04-10.xlsx
+++ b/tests/fixtures/comb_z1_2026-04-10.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="data" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="invalid_data" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="output" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="valid_data" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="calc_data" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="output" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H34"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,11 +456,6 @@
           <t>rolly_target</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>rolly_amt</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -490,9 +487,6 @@
       <c r="G2" t="n">
         <v>160</v>
       </c>
-      <c r="H2" t="n">
-        <v>160</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -524,9 +518,6 @@
       <c r="G3" t="n">
         <v>220</v>
       </c>
-      <c r="H3" t="n">
-        <v>220</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -558,9 +549,6 @@
       <c r="G4" t="n">
         <v>205</v>
       </c>
-      <c r="H4" t="n">
-        <v>205</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -592,9 +580,6 @@
       <c r="G5" t="n">
         <v>196</v>
       </c>
-      <c r="H5" t="n">
-        <v>196</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -626,9 +611,6 @@
       <c r="G6" t="n">
         <v>195</v>
       </c>
-      <c r="H6" t="n">
-        <v>195</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -660,9 +642,6 @@
       <c r="G7" t="n">
         <v>220</v>
       </c>
-      <c r="H7" t="n">
-        <v>220</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -694,9 +673,6 @@
       <c r="G8" t="n">
         <v>226</v>
       </c>
-      <c r="H8" t="n">
-        <v>226</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -728,9 +704,6 @@
       <c r="G9" t="n">
         <v>234</v>
       </c>
-      <c r="H9" t="n">
-        <v>234</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -762,9 +735,6 @@
       <c r="G10" t="n">
         <v>244</v>
       </c>
-      <c r="H10" t="n">
-        <v>244</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -796,9 +766,6 @@
       <c r="G11" t="n">
         <v>269</v>
       </c>
-      <c r="H11" t="n">
-        <v>269</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -830,9 +797,6 @@
       <c r="G12" t="n">
         <v>120</v>
       </c>
-      <c r="H12" t="n">
-        <v>120</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -864,9 +828,6 @@
       <c r="G13" t="n">
         <v>160</v>
       </c>
-      <c r="H13" t="n">
-        <v>160</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -898,9 +859,6 @@
       <c r="G14" t="n">
         <v>148</v>
       </c>
-      <c r="H14" t="n">
-        <v>148</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -932,9 +890,6 @@
       <c r="G15" t="n">
         <v>140</v>
       </c>
-      <c r="H15" t="n">
-        <v>140</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -966,9 +921,6 @@
       <c r="G16" t="n">
         <v>138</v>
       </c>
-      <c r="H16" t="n">
-        <v>138</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1000,9 +952,6 @@
       <c r="G17" t="n">
         <v>168</v>
       </c>
-      <c r="H17" t="n">
-        <v>168</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1034,9 +983,6 @@
       <c r="G18" t="n">
         <v>175</v>
       </c>
-      <c r="H18" t="n">
-        <v>175</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1068,9 +1014,6 @@
       <c r="G19" t="n">
         <v>184</v>
       </c>
-      <c r="H19" t="n">
-        <v>184</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1102,9 +1045,6 @@
       <c r="G20" t="n">
         <v>195</v>
       </c>
-      <c r="H20" t="n">
-        <v>195</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1136,9 +1076,6 @@
       <c r="G21" t="n">
         <v>220</v>
       </c>
-      <c r="H21" t="n">
-        <v>220</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1189,9 +1126,6 @@
       <c r="E23" t="n">
         <v>125</v>
       </c>
-      <c r="H23" t="n">
-        <v>125</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1220,9 +1154,6 @@
       <c r="F24" t="n">
         <v>31</v>
       </c>
-      <c r="H24" t="n">
-        <v>156</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1254,9 +1185,6 @@
       <c r="G25" t="n">
         <v>195</v>
       </c>
-      <c r="H25" t="n">
-        <v>195</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1285,9 +1213,6 @@
       <c r="F26" t="n">
         <v>125</v>
       </c>
-      <c r="H26" t="n">
-        <v>320</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1319,9 +1244,6 @@
       <c r="G27" t="n">
         <v>226</v>
       </c>
-      <c r="H27" t="n">
-        <v>226</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1350,9 +1272,6 @@
       <c r="G28" t="n">
         <v>244</v>
       </c>
-      <c r="H28" t="n">
-        <v>244</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1378,9 +1297,6 @@
       <c r="E29" t="n">
         <v>125</v>
       </c>
-      <c r="H29" t="n">
-        <v>125</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1409,9 +1325,6 @@
       <c r="F30" t="n">
         <v>31</v>
       </c>
-      <c r="H30" t="n">
-        <v>156</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1440,9 +1353,6 @@
       <c r="F31" t="n">
         <v>125</v>
       </c>
-      <c r="H31" t="n">
-        <v>125</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1471,9 +1381,6 @@
       <c r="F32" t="n">
         <v>31</v>
       </c>
-      <c r="H32" t="n">
-        <v>31</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1502,9 +1409,6 @@
       <c r="F33" t="n">
         <v>39</v>
       </c>
-      <c r="H33" t="n">
-        <v>39</v>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1534,9 +1438,6 @@
         <v>49</v>
       </c>
       <c r="G34" t="n">
-        <v>244</v>
-      </c>
-      <c r="H34" t="n">
         <v>244</v>
       </c>
     </row>
@@ -2697,4 +2598,1769 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>pertype</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>idx</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>rolly_amt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>244</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>entity</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>concept</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>period</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>pertype</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>amount</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>qrtr_target</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>rolly_target</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>idx</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>rolly_amt</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>160</v>
+      </c>
+      <c r="F2" t="n">
+        <v>40</v>
+      </c>
+      <c r="G2" t="n">
+        <v>160</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100</v>
+      </c>
+      <c r="F3" t="n">
+        <v>100</v>
+      </c>
+      <c r="G3" t="n">
+        <v>220</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>125</v>
+      </c>
+      <c r="F4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G4" t="n">
+        <v>205</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>156</v>
+      </c>
+      <c r="F5" t="n">
+        <v>31</v>
+      </c>
+      <c r="G5" t="n">
+        <v>196</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>195</v>
+      </c>
+      <c r="F6" t="n">
+        <v>39</v>
+      </c>
+      <c r="G6" t="n">
+        <v>195</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>125</v>
+      </c>
+      <c r="F7" t="n">
+        <v>125</v>
+      </c>
+      <c r="G7" t="n">
+        <v>220</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>156</v>
+      </c>
+      <c r="F8" t="n">
+        <v>31</v>
+      </c>
+      <c r="G8" t="n">
+        <v>226</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>195</v>
+      </c>
+      <c r="F9" t="n">
+        <v>39</v>
+      </c>
+      <c r="G9" t="n">
+        <v>234</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>244</v>
+      </c>
+      <c r="F10" t="n">
+        <v>49</v>
+      </c>
+      <c r="G10" t="n">
+        <v>244</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>150</v>
+      </c>
+      <c r="F11" t="n">
+        <v>150</v>
+      </c>
+      <c r="G11" t="n">
+        <v>269</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>120</v>
+      </c>
+      <c r="F12" t="n">
+        <v>30</v>
+      </c>
+      <c r="G12" t="n">
+        <v>120</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>q2019-4</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>70</v>
+      </c>
+      <c r="F13" t="n">
+        <v>70</v>
+      </c>
+      <c r="G13" t="n">
+        <v>160</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>q2020-1</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>88</v>
+      </c>
+      <c r="F14" t="n">
+        <v>18</v>
+      </c>
+      <c r="G14" t="n">
+        <v>148</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>q2020-2</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>110</v>
+      </c>
+      <c r="F15" t="n">
+        <v>22</v>
+      </c>
+      <c r="G15" t="n">
+        <v>140</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>q2020-3</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>138</v>
+      </c>
+      <c r="F16" t="n">
+        <v>28</v>
+      </c>
+      <c r="G16" t="n">
+        <v>138</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100</v>
+      </c>
+      <c r="F17" t="n">
+        <v>100</v>
+      </c>
+      <c r="G17" t="n">
+        <v>168</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>q2021-1</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>125</v>
+      </c>
+      <c r="F18" t="n">
+        <v>25</v>
+      </c>
+      <c r="G18" t="n">
+        <v>175</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>156</v>
+      </c>
+      <c r="F19" t="n">
+        <v>31</v>
+      </c>
+      <c r="G19" t="n">
+        <v>184</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>q2021-3</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>195</v>
+      </c>
+      <c r="F20" t="n">
+        <v>39</v>
+      </c>
+      <c r="G20" t="n">
+        <v>195</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>125</v>
+      </c>
+      <c r="F21" t="n">
+        <v>125</v>
+      </c>
+      <c r="G21" t="n">
+        <v>220</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>q2022-1</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>cieA</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>costs</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>q2022-2</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>156</v>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>195</v>
+      </c>
+      <c r="F23" t="n">
+        <v>39</v>
+      </c>
+      <c r="G23" t="n">
+        <v>195</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>q2020-4</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>156</v>
+      </c>
+      <c r="F24" t="n">
+        <v>31</v>
+      </c>
+      <c r="G24" t="n">
+        <v>226</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>q2021-2</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cieB</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>244</v>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="n">
+        <v>244</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cieC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>sales</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>cum</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>244</v>
+      </c>
+      <c r="F26" t="n">
+        <v>49</v>
+      </c>
+      <c r="G26" t="n">
+        <v>244</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>q2021-4</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>244</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>